--- a/output/pdf_financials_xlsx/RTO.P.xlsx
+++ b/output/pdf_financials_xlsx/RTO.P.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/RTO.P.xlsx
+++ b/output/pdf_financials_xlsx/RTO.P.xlsx
@@ -429,13 +429,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,7 +455,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -464,6 +466,16 @@
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>2027-09</t>
         </is>
       </c>
     </row>
@@ -495,6 +507,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -517,6 +539,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -539,6 +571,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -561,6 +603,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -583,6 +635,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -605,6 +667,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -627,6 +699,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -649,6 +731,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -671,6 +763,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -693,6 +795,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -715,6 +827,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -737,6 +859,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -759,6 +891,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -781,6 +923,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -803,6 +955,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -825,6 +987,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -847,6 +1019,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -869,6 +1051,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -891,6 +1083,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -913,6 +1115,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -935,6 +1147,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -957,6 +1179,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -979,6 +1211,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1001,6 +1243,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1023,6 +1275,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1045,6 +1307,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1067,6 +1339,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1089,6 +1371,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1111,6 +1403,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1136,6 +1438,16 @@
       <c r="D34" s="3" t="n">
         <v>118118</v>
       </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1154,6 +1466,16 @@
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1172,6 +1494,16 @@
       <c r="D36" s="3" t="n">
         <v>118118</v>
       </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1190,6 +1522,16 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1208,6 +1550,16 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1226,6 +1578,16 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1239,10 +1601,20 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1376</v>
+        <v>2752</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>9415</v>
+        <v>18830</v>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1257,10 +1629,20 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1376</v>
+        <v>2752</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>9415</v>
+        <v>18830</v>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1280,6 +1662,16 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1298,6 +1690,16 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1316,6 +1718,16 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1334,6 +1746,16 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1352,6 +1774,16 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1370,6 +1802,16 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1388,6 +1830,16 @@
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1410,6 +1862,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1428,6 +1890,16 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1446,6 +1918,16 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1464,6 +1946,16 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1482,6 +1974,16 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1500,6 +2002,16 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1522,6 +2034,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1540,6 +2062,16 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1558,6 +2090,16 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1576,6 +2118,16 @@
       <c r="D58" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1594,6 +2146,16 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1612,6 +2174,16 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1630,6 +2202,16 @@
       <c r="D61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1652,6 +2234,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1665,10 +2257,20 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>841659</v>
+        <v>63655</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>946982</v>
+        <v>222733</v>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1688,6 +2290,16 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1706,6 +2318,16 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1724,6 +2346,16 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1742,6 +2374,16 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1760,6 +2402,16 @@
       <c r="D68" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1778,6 +2430,16 @@
       <c r="D69" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1796,6 +2458,16 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1814,6 +2486,16 @@
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1832,6 +2514,16 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1850,6 +2542,16 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1868,6 +2570,16 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1886,6 +2598,16 @@
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1908,6 +2630,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1926,6 +2658,16 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1944,6 +2686,16 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1962,6 +2714,16 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1984,6 +2746,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -2002,6 +2774,16 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -2020,6 +2802,16 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -2038,6 +2830,16 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -2056,6 +2858,16 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -2074,6 +2886,16 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -2096,6 +2918,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -2114,6 +2946,16 @@
       <c r="D87" s="3" t="n">
         <v>-72411</v>
       </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -2132,6 +2974,16 @@
       <c r="D88" s="3" t="n">
         <v>774424</v>
       </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -2150,6 +3002,16 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -2172,6 +3034,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -2190,6 +3062,16 @@
       <c r="D91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -2208,6 +3090,16 @@
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -2226,6 +3118,16 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -2244,6 +3146,16 @@
       <c r="D94" s="3" t="n">
         <v>874571</v>
       </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2262,6 +3174,16 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -2280,6 +3202,16 @@
       <c r="D96" s="3" t="n">
         <v>874571</v>
       </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -2293,10 +3225,20 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.9984221638454529</v>
+        <v>13.20133532322677</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.9235349774335732</v>
+        <v>3.926544337839476</v>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2327,6 +3269,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -2349,6 +3301,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2371,6 +3333,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -2393,6 +3365,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -2415,6 +3397,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -2437,6 +3429,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2459,6 +3461,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -2481,6 +3493,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -2503,6 +3525,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -2525,6 +3557,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -2547,6 +3589,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -2569,6 +3621,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -2591,6 +3653,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -2613,6 +3685,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -2635,6 +3717,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -2657,6 +3749,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -2679,6 +3781,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -2701,6 +3813,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -2723,6 +3845,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -2745,6 +3877,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -2767,6 +3909,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2789,6 +3941,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2811,6 +3973,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2833,6 +4005,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2855,6 +4037,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2877,6 +4069,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2899,6 +4101,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2921,6 +4133,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2943,6 +4165,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2965,6 +4197,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -2987,6 +4229,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -3009,6 +4261,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -3031,6 +4293,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -3053,6 +4325,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -3075,6 +4357,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E133" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -3097,6 +4389,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E134" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -3115,6 +4417,16 @@
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3131,7 +4443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3176,6 +4488,16 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3203,6 +4525,16 @@
       <c r="G2" s="5" t="n">
         <v>819449</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3232,6 +4564,16 @@
       <c r="G3" s="5" t="n">
         <v>45832</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3241,7 +4583,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3251,7 +4593,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>CashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3265,6 +4607,16 @@
       <c r="G4" s="5" t="n">
         <v>118118</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3274,7 +4626,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3298,6 +4650,16 @@
       <c r="G5" s="5" t="n">
         <v>9415</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3307,7 +4669,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3327,6 +4689,16 @@
       <c r="G6" s="5" t="n">
         <v>127533</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3336,7 +4708,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3360,6 +4732,16 @@
       <c r="G7" s="5" t="n">
         <v>946982</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3369,7 +4751,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3389,6 +4771,16 @@
       <c r="G8" s="5" t="n">
         <v>-401</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3398,7 +4790,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3418,6 +4810,16 @@
       <c r="G9" s="5" t="n">
         <v>-1082</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3427,7 +4829,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>fair value through profit or loss                                                                                                                  Current assets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3449,6 +4851,16 @@
       <c r="G10" s="5" t="n">
         <v>-70928</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3480,6 +4892,16 @@
       <c r="G11" s="5" t="n">
         <v>-72411</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3513,6 +4935,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3544,6 +4976,16 @@
       <c r="G13" s="5" t="n">
         <v>874571</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3573,6 +5015,16 @@
       <c r="G14" s="5" t="n">
         <v>44602</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3602,6 +5054,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3631,6 +5093,16 @@
       <c r="G16" s="5" t="n">
         <v>774424</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3656,6 +5128,16 @@
       <c r="G17" s="5" t="n">
         <v>44602</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3681,6 +5163,16 @@
       <c r="G18" s="5" t="n">
         <v>-42618</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3699,8 +5191,10 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="n">
-        <v>-31.328</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F19" s="5" t="n">
         <v>13274</v>
@@ -3708,6 +5202,16 @@
       <c r="G19" s="5" t="n">
         <v>142765</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3737,6 +5241,16 @@
       <c r="G20" s="5" t="n">
         <v>7.49</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3746,29 +5260,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Total equity                                                                                 874,571       840,331 (pence)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
+          <t>Net asset value per ordinary share (pence) 16</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>840331</v>
+        <v>141.26</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>874571</v>
+        <v>171.65</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -3779,25 +5299,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>(pence)</t>
+          <t>£'000          £'000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Net asset value per ordinary share (pence) 16</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>141.26</v>
+        <v>44612</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>171.65</v>
+        <v>118118</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3808,12 +5342,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(pence)</t>
+          <t>£'000          £'000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Number of Ordinary Shares in issue 15</t>
+          <t>Investments Cash Debtors Creditors Sorted Holdings Convertible Loan Note1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -3823,10 +5357,20 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>594892952</v>
+        <v>316</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>509499538</v>
+        <v>316</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -3837,22 +5381,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>£'000          £'000          £'000          £'000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net gains/(losses) on investments 10 – 45,832 45,832 –</t>
+          <t>£'000          £'000          £'000          £'000 wefox Holding AG Convertible Loan Notes2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>-72.66</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-72.66</v>
-      </c>
-      <c r="G24" t="inlineStr">
+        <v>17351</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>90361</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3864,24 +5418,32 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Net losses on currency movements – (1,230) (1,230) – (33) (33) Cash and cash equivalents 11</t>
+          <t>Deep Instinct Subordinated Notes3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>22.626</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>44.612</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3893,24 +5455,30 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Net investment gains/(losses) – 44,602 44,602 – (72,693) (72,693) Other receivables 12</t>
+          <t>US Dollar 178,797 421</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>0.05</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1.376</v>
-      </c>
-      <c r="G26" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3922,24 +5490,32 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Interest income 5 834 – 834 1,127 3 1,130</t>
+          <t>Deep Instinct Convertible Loan Note4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" s="5" t="n">
-        <v>22.676</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>45.988</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>889</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3951,24 +5527,34 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Total income 834 – 834 1,127 3 1,130 Total assets</t>
+          <t>Euro 91,489 –</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" s="5" t="n">
-        <v>803.052</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>841.659</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3980,24 +5566,34 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other expenses 7 (3,230) – (3,230) (2,661) – (2,661) Advisory and management fees payable 6</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="5" t="n">
-        <v>-1.022</v>
+          <t>Other receivables</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.385</v>
-      </c>
-      <c r="G29" t="inlineStr">
+        <v>1376</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>9415</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4009,24 +5605,34 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gains/(losses) before finance (5,383) 44,602 39,219 (5,543) (72,690) (78,233) Other payables 13</t>
+          <t>Swiss Franc 13 113</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>-0.681</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>-0.9429999999999999</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4040,22 +5646,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>assets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gains/(losses) before taxation (5,383) 44,602 39,219 (5,543)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" s="5" t="n">
-        <v>-78.233</v>
+          <t>assets total</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-72.69</v>
-      </c>
-      <c r="G31" t="inlineStr">
+        <v>63655</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>222733</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4069,12 +5689,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>Assets                                                                                                                                                             following</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tax expense – – – –</t>
+          <t>US Dollar 151,968 18,841</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4083,12 +5703,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>983</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4100,20 +5726,36 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Assets                                                                                                                                                             following</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Total gains/(losses) and (5,383) 44,602 39,219 (5,543)</t>
+          <t>Euro 36,064 858</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>-78.233</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>-72.69</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4125,20 +5767,38 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Assets                                                                                                                                                             following</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>comprehensive gain/(loss) Share capital 14</t>
+          <t>£'000 £'000 Swedish Krona 120,562 264</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>860.89</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>860.89</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4152,12 +5812,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Assets                                                                                                                                                             following</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Treasury shares acquired 15</t>
+          <t>Pound Sterling (GBP) (£) £61,098 £24,542 Swiss Franc 153 107</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -4166,10 +5826,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>-0.237</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4183,22 +5855,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Assets                                                                                                                                                             following</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Basic and diluted gain/(loss) per 8 (0.90) 7.49 6.59 (0.94)</t>
+          <t>US Dollar (USD) ($) $565 $25,190 308,747 20,070</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" s="5" t="n">
-        <v>-0.01315</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.01221</v>
-      </c>
-      <c r="G36" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>984</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4210,24 +5892,32 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Ordinary Share (pence)</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Revenue reserve</t>
+          <t>(2024: 94%) of the net assets as at 30 September 2025. Cash and cash equivalents 44,612 –</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>-28.213</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-33.596</v>
+        <v>44612</v>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4239,24 +5929,32 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ordinary Share (pence)</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>accordance with International Financial Reporting Standards as adopted by the European Union (“IFRS”). Total equity</t>
+          <t>The Company’s liquidity risk is monitored by the Risk Committee in accordance with established policies, procedures and Sorted Holdings Convertible Loan Note 316 –</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>801.349</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>840.331</v>
+        <v>316</v>
       </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4268,24 +5966,30 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Ordinary Share (pence)</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The supplementary revenue and capital return columns are prepared under guidance published by the Association of Net Asset Value per Ordinary Share (pence) 16</t>
+          <t>governance structures in place. Cash flow forecasting is reviewed by the Risk Committee to ensure that the Company has sufficient cash to meet its obligations as they fall due. wefox Holding AG Convertible Loan Notes - –</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>0.13465</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.14126</v>
-      </c>
-      <c r="G39" t="inlineStr">
+        <v>17351</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>17351</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4297,24 +6001,32 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Investment Companies (“AIC”).</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Number of Ordinary Shares in issue 14</t>
+          <t>The maturity profile of the Company’s current assets and liabilities is presented in the following table. Other receivables 1,376 –</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" s="5" t="n">
-        <v>595150.414</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>594892.952</v>
+        <v>1376</v>
       </c>
       <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4323,23 +6035,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The pronouncement includes clarifying amendments Chrysalis Investment Partners LLP (“CIP LLP”)</t>
+          <t>Other current liabilities (1,328) –</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>4748</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>2369</v>
+        <v>-1328</v>
       </c>
       <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4348,27 +6072,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>operating cash flows under the indirect method.</t>
+          <t>Between       Between</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Adoption of International Financial Reporting Standards, Total advisory and management fees</t>
+          <t>Up to 3 and 12 1 and 5 44,976 –</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>4748</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2987</v>
-      </c>
-      <c r="G42" t="inlineStr">
+        <v>62327</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>17351</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4377,29 +6111,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£'000 £'000</t>
+          <t>3 months         months           years              Total</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The amendment supplements existing disclosure information in the financial statements. requirements by requiring a company to Jupiter Unit Trust Managers Limited ("JUTM")</t>
+          <t>Statement of Changes in Equity on page 78. Cash and cash equivalents 118,118 –</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>118118</v>
       </c>
       <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4408,27 +6152,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>disclose specific information about its supplier</t>
+          <t>The Company’s capital management objectives are</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>disclose specific information about its supplier finance arrangements that enables users of operating profit subtotal as the starting point for the Jupiter Investment Management Limited ("JIML")</t>
+          <t>Sorted Holdings Convertible Loan Note 316 –</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>3.998</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.618</v>
+        <v>316</v>
       </c>
       <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4437,44 +6193,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>The Company’s capital management objectives are</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Investments held at fair value through profit or loss 10</t>
+          <t>•    to ensure that it is able to continue as a going concern; and wefox Holding AG Convertible Loan Notes – 90,361</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>780.376</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>795671</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>819449</v>
+        <v>90361</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Company’s capital. These reviews include</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net gains on investments held at 10 – 131,028 131,028 –</t>
+          <t>Other receivables 9,415 –</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4484,26 +6254,38 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>45832</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>45832</v>
+        <v>9415</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Company’s capital. These reviews include</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Net losses on currency movements – (1,537) (1,537) – (1,230) (1,230) Cash and cash equivalents 11</t>
+          <t>• the extent to which revenue reserves should be retained or utilised; and Loans and borrowings – (70,928)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4513,26 +6295,38 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>44612</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>118118</v>
+        <v>-70928</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Company’s capital. These reviews include</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net investment gains – 129,491 129,491 – 44,602 44,602 Other receivables 12</t>
+          <t>Other current liabilities (1,483) –</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4542,26 +6336,38 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1376</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>9415</v>
+        <v>-1483</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Company’s capital. These reviews include</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Interest income 5 4,099 – 4,099 834 – 834</t>
+          <t>Company’s capital. These reviews include total</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4571,26 +6377,36 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>45988</v>
+        <v>150322</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>127533</v>
+        <v>4523</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Other income 2,591 2,591 – – – Total assets</t>
+          <t>Total Directors’ fees charged</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4600,26 +6416,36 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>841659</v>
+        <v>398</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>946982</v>
+        <v>478</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Advisory and management fees 6 (4,748) – (4,748) (2,987) – (2,987) Advisory and management fees payable</t>
+          <t>Andrew Haining</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4629,26 +6455,36 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-385</v>
+        <v>0.0133</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-401</v>
+        <v>79000</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Other expenses 7 (3,115) – (3,115) (3,230) – (3,230) Other payables 13</t>
+          <t>Directors’ fees outstanding</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4657,27 +6493,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>-943</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-1082</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>fair value through profit or loss Current assets</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gains/(losses) before finance (1,173) 129,491 128,318 (5,383) 44,602 39,219 Loans and borrowings 14</t>
+          <t>Stephen Coe</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4686,56 +6536,76 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" s="5" t="n">
+        <v>0.0102</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-70928</v>
+        <v>60909</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>As at 30 September 2025 the following Directors had holdings in the Company: Simon Holden</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>-1.703</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-1328</v>
+        <v>0.015</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-72411</v>
+        <v>89500</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Finance costs 14 (7,849) – (7,849) –</t>
+          <t>Anne Ewing</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4744,12 +6614,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="5" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4758,44 +6634,56 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>Directors’ fees                                                                                                                                                          Director</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Net assets</t>
+          <t>Tim Cruttenden</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>801.349</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>840331</v>
+        <v>0.0036</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>874571</v>
+        <v>21298</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>% Ordinary Shares</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gains/(losses) before taxation (9,022) 129,491 120,469 (5,383)</t>
+          <t>Number of outstanding as at Margaret O’Connor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4804,23 +6692,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>39219</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>44602</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ordinary Shares      30 September 2025</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tax expense – – – –</t>
+          <t>S Cruttenden (son of Tim Cruttenden)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4829,12 +6735,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="5" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>11170</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4843,13 +6755,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Share capital 15</t>
+          <t>20. Post Balance Sheet Events Andrew Haining</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4859,22 +6775,36 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>860653</v>
+        <v>0.0155</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>774424</v>
+        <v>79000</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Total gains/(losses) and (9,022) 129,491 120,469 (5,383)</t>
+          <t>Tim Cruttenden</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4884,22 +6814,36 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>39219</v>
+        <v>0.0042</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>44602</v>
+        <v>21298</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>gain/(loss) comprehensive Revenue reserve</t>
+          <t>S Cruttenden (son of Tim Cruttenden)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4909,179 +6853,251 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-33596</v>
+        <v>0.0022</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-42618</v>
+        <v>11170</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Capital reserve</t>
+          <t>Net gains/(losses) on investments 10 – 45,832 45,832 –</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>-31.328</v>
+        <v>-72.66</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>13274</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>142765</v>
+        <v>-72.66</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>held at fair value                                                                                                                              Current assets</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gain/(loss) per Ordinary Share 8 (1.65) 23.74 22.09 (0.90)</t>
+          <t>Net losses on currency movements – (1,230) (1,230) – (33) (33) Cash and cash equivalents 11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="5" t="n">
+        <v>22.626</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>7.49</v>
+        <v>44.612</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>held at fair value                                                                                                                              Current assets</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Total equity</t>
+          <t>Net investment gains/(losses) – 44,602 44,602 – (72,693) (72,693) Other receivables 12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>840331</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>874571</v>
+        <v>1.376</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(pence)</t>
+          <t>held at fair value                                                                                                                              Current assets</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Net asset value per ordinary share (pence) 16</t>
+          <t>Interest income 5 834 – 834 1,127 3 1,130</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="5" t="n">
+        <v>22.676</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>141.26</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>171.65</v>
+        <v>45.988</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(pence)</t>
+          <t>held at fair value                                                                                                                              Current assets</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Number of Ordinary Shares in issue 15</t>
+          <t>Total income 834 – 834 1,127 3 1,130 Total assets</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>803.052</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>594892952</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>509499538</v>
+        <v>841.659</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>held at fair value                                                                                                                              Current assets</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net gains/(losses) on investments 10 – 45,832 45,832 –</t>
+          <t>Other expenses 7 (3,230) – (3,230) (2,661) – (2,661) Advisory and management fees payable 6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>-72.66</v>
+        <v>-1.022</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-72.66</v>
+        <v>-0.385</v>
       </c>
       <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5090,27 +7106,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>held at fair value Current assets</t>
+          <t>held at fair value                                                                                                                              Current assets</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net losses on currency movements – (1,230) (1,230) – (33) (33) Cash and cash equivalents 11</t>
+          <t>Gains/(losses) before finance (5,383) 44,602 39,219 (5,543) (72,690) (78,233) Other payables 13</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>22.626</v>
+        <v>-0.681</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>44.612</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5119,27 +7145,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>held at fair value Current assets</t>
+          <t>costs and taxation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net investment gains/(losses) – 44,602 44,602 – (72,693) (72,693) Other receivables 12</t>
+          <t>Gains/(losses) before taxation (5,383) 44,602 39,219 (5,543)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>0.05</v>
+        <v>-78.233</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>1.376</v>
+        <v>-72.69</v>
       </c>
       <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5148,27 +7184,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>held at fair value Current assets</t>
+          <t>costs and taxation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Interest income 5 834 – 834 1,127 3 1,130</t>
+          <t>Tax expense – – – –</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>22.676</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>45.988</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5177,27 +7227,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Total income 834 – 834 1,127 3 1,130 Total assets</t>
+          <t>Total gains/(losses) and (5,383) 44,602 39,219 (5,543)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>803.052</v>
+        <v>-78.233</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>841.659</v>
+        <v>-72.69</v>
       </c>
       <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5206,27 +7262,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>held at fair value Current assets</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Other expenses 7 (3,230) – (3,230) (2,661) – (2,661) Advisory and management fees payable 6</t>
+          <t>comprehensive gain/(loss) Share capital 14</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>-1.022</v>
+        <v>860.89</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.385</v>
+        <v>860.89</v>
       </c>
       <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5235,27 +7297,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>held at fair value Current assets</t>
+          <t>for the year</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gains/(losses) before finance (5,383) 44,602 39,219 (5,543) (72,690) (78,233) Other payables 13</t>
+          <t>Treasury shares acquired 15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>-0.681</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.237</v>
       </c>
       <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5264,27 +7338,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>for the year</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gains/(losses) before taxation (5,383) 44,602 39,219 (5,543)</t>
+          <t>Basic and diluted gain/(loss) per 8 (0.90) 7.49 6.59 (0.94)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>-78.233</v>
+        <v>-0.01315</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-72.69</v>
+        <v>-0.01221</v>
       </c>
       <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5293,31 +7377,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>costs and taxation</t>
+          <t>for the year</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tax expense – – – –</t>
+          <t>Ordinary Share (pence) Capital reserve</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>-31.328</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>13.274</v>
       </c>
       <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5326,23 +7416,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>for the year</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Total gains/(losses) and (5,383) 44,602 39,219 (5,543)</t>
+          <t>Revenue reserve</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>-78.233</v>
+        <v>-28.213</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-72.69</v>
+        <v>-33.596</v>
       </c>
       <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5351,23 +7455,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>for the year</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>comprehensive gain/(loss) Share capital 14</t>
+          <t>accordance with International Financial Reporting Standards as adopted by the European Union (“IFRS”). Total equity</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>860.89</v>
+        <v>801.349</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>860.89</v>
+        <v>840.331</v>
       </c>
       <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5376,7 +7494,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5386,19 +7504,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Treasury shares acquired 15</t>
+          <t>The supplementary revenue and capital return columns are prepared under guidance published by the Association of Net Asset Value per Ordinary Share (pence) 16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="5" t="n">
+        <v>0.13465</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.237</v>
+        <v>0.14126</v>
       </c>
       <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5407,27 +7533,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Investment Companies (“AIC”).</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Basic and diluted gain/(loss) per 8 (0.90) 7.49 6.59 (0.94)</t>
+          <t>Number of Ordinary Shares in issue 14</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-0.01315</v>
+        <v>595150.414</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.01221</v>
+        <v>594892.952</v>
       </c>
       <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5441,22 +7577,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ordinary Share (pence)</t>
+          <t>The Company generates liquidity by raising capital</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Revenue reserve</t>
+          <t>The Directors' going concern assessment includes cycle. Andrew Haining</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>-28.213</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-33.596</v>
+        <v>0.0155</v>
       </c>
       <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>79000</v>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5470,22 +7616,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ordinary Share (pence)</t>
+          <t>The Company generates liquidity by raising capital</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>accordance with International Financial Reporting Standards as adopted by the European Union (“IFRS”). Total equity</t>
+          <t>consideration of a range of likely downside scenarios • The Company honours the committed capital return Stephen Coe</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>801.349</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>840.331</v>
+        <v>0.012</v>
       </c>
       <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>60909</v>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5499,22 +7655,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ordinary Share (pence)</t>
+          <t>The Company generates liquidity by raising capital</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>The supplementary revenue and capital return columns are prepared under guidance published by the Association of Net Asset Value per Ordinary Share (pence) 16</t>
+          <t>which measure the impact on the Company’s liquidity                                                         under the CAP and does not raise further capital.                                                                                                                              Simon Holden                                                                    89,500               0.0176of differing assumptions for portfolio valuation, exits, follow-on investment requirements, the settlement of • The Company repays the Barclays debt facility. Anne Ewing</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>0.13465</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.14126</v>
+        <v>0.0108</v>
       </c>
       <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5528,25 +7694,1685 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Investment Companies (“AIC”).</t>
+          <t>The Company generates liquidity by raising capital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Number of Ordinary Shares in issue 14</t>
+          <t>the inability to make portfolio exits.                                               Margaret O’Connor                                                                           -                   -Directors have also considered the proposals to maximise value and returns for shareholders, exploring opportunities • A sustained period of inflation of approximately 10% S Cruttenden (son of Tim Cruttenden)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>595150.414</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>594892.952</v>
+        <v>0.0022</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>11170</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>The Company generates liquidity by raising capital</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>the going concern basis in preparing them.                   10 March 2026 (2024: £nil). This available liquidity would sustain the business over the course of the viability period. Andrew Haining</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>79000</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>The Company generates liquidity by raising capital</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>The Directors have assessed the viability of the Company considered the proposals to maximise value and returns Simon Holden</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>89500</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>The Company generates liquidity by raising capital</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>over the three-year period to September 2028. The            for shareholders, exploring opportunities for realisations                                                                                                                            Anne Ewing                                                                       55,000             0.0092Directors consider that three years is an appropriate         over a three-year time horizon. period to assess viability given the Company’s style of Tim Cruttenden 21,298 0.0036 The Directors, having considered the above and havinginvestment and is a sufficient investment time horizon to carried out a robust assessment of the principal and Margaret O’Connor - -be relevant to shareholders. emerging risks facing the Company, have concluded that S Cruttenden (son of Tim Cruttenden)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>11170</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Company and its portfolio.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>58 Chrysalis Investments Limited Corporate Governance Annual Report and Audited Financial Statements</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>of ESG analysis into the investment process.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>60 Chrysalis Investments Limited Corporate Governance Annual Report and Audited Financial Statements</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Company itself.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>62 Chrysalis Investments Limited Corporate Governance Annual Report and Audited Financial Statements</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>In accordance with the Company’s Articles of</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>(Risk Class 11: Valuation)                                                     Simon Holden                                                                    89,500              0.0150continuation of the Company. The Board recommended that Shareholders vote in favour of continuation and such • The ongoing expenses of the Company Anne Ewing</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>9.2e-06</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>In accordance with the Company’s Articles of</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>resolution was duly passed. The Directors will now put a further Continuation Resolution to Shareholders at the The Directors’ considered a severe downside scenario Tim Cruttenden</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>21.298</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>3.6e-06</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>In accordance with the Company’s Articles of</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Annual General Meeting of the Company every three which models: Margaret O’Connor</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>years thereafter.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>• A significant economic event, which results in a S Cruttenden (son of Tim Cruttenden)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>1.9e-06</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>years thereafter.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Andrew Haining                                                                    79,000               0.0133drawn.                                                        •   Dislocation of public and private markets, including the prolonged closure of the IPO market, resulting in Stephen Coe</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>60.909</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>1.02e-05</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>years thereafter.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Taking all matters into account, the Directors have a              the inability to make portfolio exits. reasonable expectation that the Company will continue in Simon Holden</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>1.5e-05</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>years thereafter.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Financial Statements, and continue to adopt the going                                                                                    Tim Cruttenden                                                                             21,298             0.0036                                                   The Directors, having considered the above and having concern basis in preparing them. carried out a robust assessment of the principal and Margaret O’Connor</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2027.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>60 Chrysalis Investments Limited Corporate Governance Annual Report and Audited Financial Statements</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>generation of long term sustainable value.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>62 Chrysalis Investments Limited Corporate Governance Annual Report and Audited Financial Statements</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Director.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>64 Chrysalis Investments Limited Corporate Governance Annual Report and Audited Financial Statements</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>(continued)                                                Statements</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Classification of Liabilities as Current or Non-current 1 January 2027, subject to adoption by the European</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>2.023</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Statements)                                                                                                                                                                                                                                       £'000          £'000</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>following key new requirements:                                                            Interest on assets held at amortised cost:    The amendments aim to promote consistency in position, debt and other liabilities with an uncertain of profit or loss, namely the operating, investing, UK treasury bills</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.872</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Statements)                                                                                                                                                                                                                                       £'000          £'000</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>settlement date should be classified as current (due                                                                       financing, discontinued operations and income tax or potentially due to be settled within one year) or categories. Entities are also required to present a</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>non-current.                                                               newly-defined operating profit subtotal. Entities' net</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>(Effective for reporting periods beginning on or after financial statements.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>2.023</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1 January 2024)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>The amendment supplements existing disclosure                information in the financial statements. requirements by requiring a company to Jupiter Unit Trust Managers Limited ("JUTM")</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1 January 2024)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>cash flows under the indirect method.                                                    Chrysalis Investment Partners LLP ("CIP LLP")                                                   2,369           –    arrangements on the company’s liabilities and cash flows and on the company’s exposure to liquidity risk. The Company is still in the process of assessing the impact Total advisory and management fees</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>4.009</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Advisory and management fees</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>The Company paid a monthly “Management Fee” to JIML, equal to 1/12 of 0.5% of the Net Asset Value up to 30</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>2.023</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>– audit fees (current year)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2024 to 30 September 2024) are charged to Revenue in the Statement of Comprehensive Income. – audit fees ((over)/under accrual in prior year)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Performance Fee – non-audit fees</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>To 31 March 2024, the performance fee payable is the sum of which is equal to 20% of the amount by which the Adjusted Committee fees</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Water Mark (the “Performance Fee”). Depositary fees</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>At an Extraordinary General meeting that took place on 15 March 2024, new Performance Fee terms were approved. Directors' expenses</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>The revised Performance Fee, effective from 1 April 2024, is the sum of which shall be equal to 12.5 per cent of the amount by which the Adjusted Net Asset Value at the end of a Calculation Period exceeds the higher of: (i) the Performance Directors' fees</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0.433</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hurdle; and (ii) the High Water Mark. The last Performance Fee was payable for the period ended 30 September 2021, at which time the NAV per share was 251.96 pence (2024: 141.26 pence). A full definition of the terms of the new Directors' liability insurance</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>5.9e-05</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>6.8e-05</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Management Fee over the period.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FCA fees</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees: accrual (30 September 2023: £nil) for performance fees has been charged within these Audited Financial Statements. – ongoing operations</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>– valuation fees</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>– due diligence fees</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>– fees relating to purchases of investments</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>0.516</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Design fees</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" s="5" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Registrars' fees</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" s="5" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Secretarial fees</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sundry</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Legal fee and professional fees total</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>2.661</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/RTO.P.xlsx
+++ b/output/pdf_financials_xlsx/RTO.P.xlsx
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
